--- a/AAII_Financials/Yearly/JRONY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/JRONY_YR_FIN.xlsx
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>177300</v>
+        <v>173800</v>
       </c>
       <c r="E47" s="3">
         <v>89000</v>
